--- a/ky/downloads/data-excel/5.6.1.1.xlsx
+++ b/ky/downloads/data-excel/5.6.1.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F1CD34-D210-4771-8961-F816B65A432C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -181,7 +182,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -337,9 +338,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -387,13 +388,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -416,11 +411,11 @@
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Normal_PPI" xfId="3"/>
+    <cellStyle name="Normal_PPI" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="2"/>
-    <cellStyle name="Обычный 3" xfId="1"/>
-    <cellStyle name="Обычный_80102" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный_80102" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -436,9 +431,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -476,9 +471,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -513,7 +508,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -548,7 +543,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -721,7 +716,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
@@ -796,13 +791,13 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D6" s="14"/>
@@ -850,13 +845,13 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="22" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="15"/>
@@ -867,10 +862,10 @@
       <c r="A10" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="15">
@@ -890,7 +885,7 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="15">
@@ -910,7 +905,7 @@
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="17" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="15">
@@ -930,7 +925,7 @@
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="15">
@@ -950,7 +945,7 @@
       <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="17" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="15">
@@ -970,7 +965,7 @@
       <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="15">
@@ -990,7 +985,7 @@
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="15">
@@ -1004,13 +999,13 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="17" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="15">
@@ -1024,33 +1019,33 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" thickBot="1">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="20">
         <v>98.5</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="20">
         <v>99.5</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="20">
         <v>97.4</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="22.5">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="23" t="s">
         <v>53</v>
       </c>
     </row>
